--- a/data/filtered/china_sports.xlsx
+++ b/data/filtered/china_sports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>2008-08-08</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3173528/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2001-07-12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1297747/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2013-08-16</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20388223/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1424631/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>2024-02-10</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36369452/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>2024-02-10</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36081094/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>2016-09-02</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5446197/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>2011-12-09</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5244092/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/37311135/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2015-08-07</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25853727/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35030151/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>2015-12-04</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25809384/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30128916/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30163509/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>1982-01-21</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1297213/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>2023-01-24</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30323380/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35882742/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2021-09-04</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/32568661/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35608160/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>1983-10-13</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299497/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>1987-08-12</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307979/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307321/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303341/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30391228/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>2013-02-08</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11599168/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>2010-06-22</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3074503/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1434171/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>2008-05-17</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2144584/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>2010-08-13</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4202326/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25903033/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>2017-04-07</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26704592/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>2008-05-09</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3024072/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>2019-08-23</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30328825/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>2006-11-10</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1931425/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>2020-12-30</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35207868/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>2008-03-11</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2972591/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>2010-09-10</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4022126/</t>
         </is>
@@ -2015,7 +2595,22 @@
           <t>2021-01-15</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34834554/</t>
         </is>
@@ -2056,7 +2651,22 @@
           <t>2008-06-19</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3006599/</t>
         </is>
@@ -2097,7 +2707,22 @@
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27006898/</t>
         </is>
@@ -2138,7 +2763,22 @@
           <t>2008-02-08</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1950525/</t>
         </is>
@@ -2179,7 +2819,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2407373/</t>
         </is>
@@ -2220,7 +2875,22 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36088962/</t>
         </is>
@@ -2261,7 +2931,22 @@
           <t>2013-07-18</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5919333/</t>
         </is>
@@ -2302,7 +2987,22 @@
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6946777/</t>
         </is>
@@ -2343,7 +3043,22 @@
           <t>2016-05-21</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26765405/</t>
         </is>
@@ -2384,7 +3099,22 @@
           <t>2019-10-07</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33447759/</t>
         </is>
@@ -2425,7 +3155,22 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3123961/</t>
         </is>
@@ -2466,7 +3211,22 @@
           <t>1985-05-04</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1906974/</t>
         </is>
@@ -2507,7 +3267,22 @@
           <t>2009-04-02</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3619071/</t>
         </is>
@@ -2548,7 +3323,22 @@
           <t>2017-08-14</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27119392/</t>
         </is>
@@ -2589,7 +3379,22 @@
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34927952/</t>
         </is>
@@ -2630,7 +3435,22 @@
           <t>1964</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2238329/</t>
         </is>
@@ -2671,7 +3491,22 @@
           <t>2010-07-06</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2276989/</t>
         </is>
@@ -2712,7 +3547,22 @@
           <t>1997-06-27</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308315/</t>
         </is>
@@ -2753,7 +3603,22 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3210953/</t>
         </is>
@@ -2794,7 +3659,22 @@
           <t>2021-06-12</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34917447/</t>
         </is>
@@ -2835,7 +3715,22 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25958824/</t>
         </is>
@@ -2876,7 +3771,22 @@
           <t>2006-04-07</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1877568/</t>
         </is>
@@ -2917,7 +3827,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21769324/</t>
         </is>
@@ -2958,7 +3883,22 @@
           <t>2020-10-16</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34454770/</t>
         </is>
@@ -2999,7 +3939,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464156/</t>
         </is>
@@ -3040,7 +3995,22 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30434811/</t>
         </is>
@@ -3081,7 +4051,22 @@
           <t>2012-10-14</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19977901/</t>
         </is>
@@ -3122,7 +4107,22 @@
           <t>2020-04-05</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35017520/</t>
         </is>
@@ -3163,7 +4163,22 @@
           <t>2017-09-09</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27069788/</t>
         </is>
@@ -3204,7 +4219,22 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35505608/</t>
         </is>
@@ -3245,7 +4275,22 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35198422/</t>
         </is>
@@ -3286,7 +4331,22 @@
           <t>2019-11-08</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27132180/</t>
         </is>
@@ -3327,7 +4387,22 @@
           <t>2012-08-31</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10799138/</t>
         </is>
@@ -3368,7 +4443,22 @@
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34822225/</t>
         </is>
@@ -3409,7 +4499,22 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4051856/</t>
         </is>
@@ -3450,7 +4555,22 @@
           <t>2020-03-24</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34926591/</t>
         </is>
@@ -3491,7 +4611,22 @@
           <t>2014-01-21</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20381251/</t>
         </is>
@@ -3532,7 +4667,22 @@
           <t>2011-07-29</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5319803/</t>
         </is>
@@ -3573,7 +4723,22 @@
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35739930/</t>
         </is>
@@ -3614,7 +4779,22 @@
           <t>2021-01-15</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30279972/</t>
         </is>
@@ -3655,7 +4835,22 @@
           <t>2019-06-14</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26587411/</t>
         </is>
@@ -3696,7 +4891,22 @@
           <t>2018-07-03</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30242130/</t>
         </is>
@@ -3737,7 +4947,22 @@
           <t>2022-03-25</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34833903/</t>
         </is>
@@ -3778,7 +5003,22 @@
           <t>2016-09-16</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26844130/</t>
         </is>
@@ -3819,7 +5059,22 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26774018/</t>
         </is>
@@ -3860,7 +5115,22 @@
           <t>2008-04-26</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2417346/</t>
         </is>
@@ -3901,7 +5171,22 @@
           <t>2017-07-30</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27098659/</t>
         </is>
@@ -3942,7 +5227,22 @@
           <t>2013-11-26</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25768227/</t>
         </is>
@@ -3983,7 +5283,22 @@
           <t>2016-09-02</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26413404/</t>
         </is>
@@ -4024,7 +5339,22 @@
           <t>2016-11-04</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26547005/</t>
         </is>
@@ -4065,7 +5395,22 @@
           <t>2013-09-30</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5044748/</t>
         </is>
